--- a/data/Spring2026/Thesis/Appendix/Fig 2/Missing, a 0.002/DB1_missing-values_a0.002_output.xlsx
+++ b/data/Spring2026/Thesis/Appendix/Fig 2/Missing, a 0.002/DB1_missing-values_a0.002_output.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kdahlqui\Desktop\Yeast Genetics 2026\DB1-2-5 Comparison\DB1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479ADC68-DDFF-4147-95E0-82A9F5E0E3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" tabRatio="500" firstSheet="23" activeTab="27"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="production_rates" sheetId="4" r:id="rId1"/>
@@ -41,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="59">
   <si>
     <t>ABF1</t>
   </si>
@@ -223,7 +229,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -473,14 +479,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -490,7 +494,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="132" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="132" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="133"/>
   </cellXfs>
   <cellStyles count="134">
@@ -625,9 +629,9 @@
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="5"/>
-    <cellStyle name="Normal 3" xfId="132"/>
-    <cellStyle name="Normal 4" xfId="133"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="Normal 3" xfId="132" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="Normal 4" xfId="133" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -963,146 +967,146 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.875" style="2"/>
+    <col min="1" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.15759999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>0.22359999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>0.308</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>0.43319999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>0.20100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>0.1026</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>0.32240000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>0.27179999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>0.4078</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>0.69320000000000004</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>0.28299999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>0.17319999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>0.72960000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>0.1042</v>
       </c>
     </row>
@@ -1118,906 +1122,908 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
         <v>1</v>
       </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2">
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>1</v>
       </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
         <v>1</v>
       </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2">
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2">
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>1</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>1</v>
       </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>1</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>1</v>
       </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
         <v>1</v>
       </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2">
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>1</v>
       </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2">
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
         <v>1</v>
       </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2">
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
         <v>1</v>
       </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="2">
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
         <v>1</v>
       </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2">
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
         <v>1</v>
       </c>
-      <c r="M13" s="2">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="2">
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2">
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="M14" s="2">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="2">
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>1</v>
       </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2">
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
         <v>1</v>
       </c>
-      <c r="M15" s="2">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2">
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
         <v>1</v>
       </c>
-      <c r="O15" s="2">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="2">
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2">
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>1</v>
       </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2">
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
         <v>1</v>
       </c>
-      <c r="O16" s="2">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="2">
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2">
-        <v>0</v>
-      </c>
-      <c r="O17" s="2">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="2">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2032,196 +2038,196 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.875" style="2"/>
+    <col min="1" max="1" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>2E-3</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>100000000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>100000000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>15</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>30</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>10</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>15</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>20</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="1">
         <v>25</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>30</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
         <v>35</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>40</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="1">
         <v>45</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>50</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="1">
         <v>55</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="1">
         <v>60</v>
       </c>
     </row>
@@ -2237,146 +2243,146 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.875" style="2"/>
+    <col min="1" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2391,7 +2397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3149,7 +3155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3907,7 +3913,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4665,7 +4671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5423,7 +5429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6181,7 +6187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6939,7 +6945,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7187,162 +7193,162 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="11" style="10"/>
+    <col min="1" max="16384" width="11" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="11"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
         <v>7.8799999999999995E-2</v>
       </c>
-      <c r="D2" s="11"/>
+      <c r="D2" s="9"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>0.1118</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>0.154</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>0.21659999999999999</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>0.10050000000000001</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>0.16120000000000001</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>0.13589999999999999</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="12">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="9"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>0.2039</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>0.34660000000000002</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>0.14149999999999999</v>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>8.6599999999999996E-2</v>
       </c>
-      <c r="D15" s="15"/>
+      <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>0.36480000000000001</v>
       </c>
-      <c r="D16" s="15"/>
+      <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>5.21E-2</v>
       </c>
     </row>
@@ -7353,7 +7359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7601,7 +7607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7849,7 +7855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8097,7 +8103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8345,7 +8351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8593,7 +8599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8739,7 +8745,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8885,11 +8891,14 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>39</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -9793,7 +9802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10239,760 +10248,751 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1">
         <v>15</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>15</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <v>15</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="1">
         <v>15</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1">
         <v>30</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="1">
         <v>30</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <v>30</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="1">
         <v>30</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <v>30</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="1">
         <v>60</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="1">
         <v>60</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="1">
         <v>60</v>
       </c>
-      <c r="N1" s="2">
+      <c r="N1" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
         <v>-2.1071</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>-0.89259999999999995</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>-2.1899999999999999E-2</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>-1.7297</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>-1.2332000000000001</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>-0.43809999999999999</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="5">
         <v>-1.9801</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>-0.87129999999999996</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="5">
         <v>-1.3866000000000001</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="5">
         <v>-2.4279999999999999</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="5">
         <v>-0.65590000000000004</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="5">
         <v>-3.0996999999999999</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="5">
         <v>-1.4733000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>0.6139</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>-1.0689</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>0.19059999999999999</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>-0.39800000000000002</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>0.5827</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="7">
+      <c r="G3" s="6"/>
+      <c r="H3" s="5">
         <v>-0.3947</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>-0.62639999999999996</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="5">
         <v>0.3377</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="5">
         <v>0.81699999999999995</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="5">
         <v>0.55659999999999998</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="5">
         <v>-0.43569999999999998</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="5">
         <v>-1.2497</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>-0.64400000000000002</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>1.6657999999999999</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>-0.70330000000000004</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>0.1053</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>0.45</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="7">
+      <c r="G4" s="6"/>
+      <c r="H4" s="5">
         <v>1.3611</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>-0.46939999999999998</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <v>-0.44219999999999998</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>0.79820000000000002</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <v>-0.13619999999999999</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="5">
         <v>1.0173000000000001</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="5">
         <v>-0.46479999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>-1.9464999999999999</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>-0.13730000000000001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>-0.2276</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>0.73680000000000001</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>-1.5017</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>-1.9844999999999999</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <v>-1.3883000000000001</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>0.16520000000000001</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>-0.72529999999999994</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="5">
         <v>-1.7791999999999999</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="5">
         <v>-1.901</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="5">
         <v>-0.67159999999999997</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="5">
         <v>-1.595</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>0.97</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>0.30430000000000001</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>-0.99039999999999995</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>-0.2636</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>-0.38200000000000001</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>0.42059999999999997</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <v>-0.49109999999999998</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>-0.12839999999999999</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <v>-0.72360000000000002</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="5">
         <v>-1.3476999999999999</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <v>-1.0468</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="5">
         <v>-1.0978000000000001</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="5">
         <v>-0.92479999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>-0.13730000000000001</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>-9.9699999999999997E-2</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>1.2385999999999999</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>1.3909</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>-0.4224</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>0.54610000000000003</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <v>1.0285</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <v>1.2338</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <v>2.2159</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="5">
         <v>2.1796000000000002</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="5">
         <v>0.84470000000000001</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="5">
         <v>2.4687000000000001</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="5">
         <v>1.4784999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>1.1491</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>0.1163</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>1.3471</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>-1.4533</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>-8.2100000000000006E-2</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <v>1.083</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="5">
         <v>0.62070000000000003</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <v>-0.13400000000000001</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="5">
         <v>-0.56620000000000004</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="5">
         <v>0.248</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="5">
         <v>0.14849999999999999</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="5">
         <v>0.5675</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="5">
         <v>5.5500000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>-1.3141</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>0.39389999999999997</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>0.1439</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>-0.51329999999999998</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>-0.70040000000000002</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="5">
         <v>-0.2467</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="5">
         <v>1.4085000000000001</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="5">
         <v>0.97330000000000005</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="5">
         <v>0.65039999999999998</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="5">
         <v>0.20250000000000001</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="5">
         <v>0.89239999999999997</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="5">
         <v>0.90069999999999995</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="5">
         <v>0.1953</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>0.51380000000000003</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>1.9214</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>-0.88590000000000002</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>-2.6541999999999999</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>0.13800000000000001</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="5">
         <v>1.5184</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="5">
         <v>0.27939999999999998</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <v>-2.5135000000000001</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <v>-1.1181000000000001</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="5">
         <v>0.2225</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="5">
         <v>-1.0353000000000001</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="5">
         <v>-0.2074</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="5">
         <v>-1.8463000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>0.30580000000000002</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>0.2392</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>1.8398000000000001</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>1.2493000000000001</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>-0.95250000000000001</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <v>1.405</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <v>1.3109</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="5">
         <v>1.2568999999999999</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="5">
         <v>1.9007000000000001</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="5">
         <v>1.4816</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="5">
         <v>0.93799999999999994</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="5">
         <v>1.8391</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="5">
         <v>2.2172000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>-1.0625</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>0.92459999999999998</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>0.1666</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>-0.26960000000000001</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>0.35849999999999999</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>0.95140000000000002</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <v>0.12330000000000001</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>1.2802</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="5">
         <v>-0.68079999999999996</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="5">
         <v>0.76339999999999997</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="5">
         <v>1.3451</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="5">
         <v>0.83550000000000002</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="5">
         <v>-0.12709999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>3.0700000000000002E-2</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>2.1524999999999999</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>1.2788999999999999</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>-0.4526</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>0.69169999999999998</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <v>0.53420000000000001</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="5">
         <v>2.2597999999999998</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <v>-0.92320000000000002</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="5">
         <v>0.82930000000000004</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="5">
         <v>1.3828</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="5">
         <v>0.90039999999999998</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="5">
         <v>0.88880000000000003</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="5">
         <v>-1.0367</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>-0.92859999999999998</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>-2.3E-2</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>-0.36509999999999998</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>-0.32779999999999998</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>-0.4798</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>0.20469999999999999</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <v>0.32219999999999999</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>-0.23769999999999999</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <v>-0.63690000000000002</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="5">
         <v>-1.4226000000000001</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="5">
         <v>-0.52939999999999998</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="5">
         <v>0.29959999999999998</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="5">
         <v>0.28120000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>-1.1269</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>-0.21</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>-0.66759999999999997</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>-1.6963999999999999</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>-0.34960000000000002</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <v>1.2371000000000001</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="5">
         <v>0.94320000000000004</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>-0.36209999999999998</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="5">
         <v>-1.8086</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="5">
         <v>0.66169999999999995</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="5">
         <v>0.61919999999999997</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="5">
         <v>0.20499999999999999</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="5">
         <v>-0.72499999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>-0.20250000000000001</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>-1.0587</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>-0.64019999999999999</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>-2.2532000000000001</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>-8.3000000000000004E-2</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>-1.6116999999999999</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <v>-0.104</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>-0.1487</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <v>-0.93940000000000001</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="5">
         <v>-0.59009999999999996</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="5">
         <v>0.13289999999999999</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="5">
         <v>-0.72219999999999995</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="5">
         <v>-0.51170000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>0.65939999999999999</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>0.61350000000000005</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>0.32379999999999998</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>-0.37119999999999997</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <v>1.4712000000000001</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="5">
         <v>1.9049</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="5">
         <v>0.59899999999999998</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <v>-0.2354</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="5">
         <v>-0.39400000000000002</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="5">
         <v>2.9605999999999999</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="5">
         <v>3.5569000000000002</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="5">
         <v>1.3863000000000001</v>
       </c>
-      <c r="N17" s="8"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G20" s="1"/>
+      <c r="N17" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11006,689 +11006,689 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.875" style="2"/>
+    <col min="1" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1">
         <v>15</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>15</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <v>15</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="1">
         <v>15</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1">
         <v>30</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="1">
         <v>30</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <v>30</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="1">
         <v>30</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <v>60</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="1">
         <v>60</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="1">
         <v>60</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
         <v>-1.361</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>-0.1381</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>-1.1930000000000001</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>-1.4638</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>0.35110000000000002</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>-0.73199999999999998</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="5">
         <v>-0.90820000000000001</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>-1.0192000000000001</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="5">
         <v>-2.0072999999999999</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="5">
         <v>-0.2404</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="5">
         <v>-0.57550000000000001</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="5">
         <v>-2.6553</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>-0.17180000000000001</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>-0.2792</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>-0.17519999999999999</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>-0.68840000000000001</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>-0.24360000000000001</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>0.15809999999999999</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>-0.42530000000000001</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7">
+      <c r="I3" s="6"/>
+      <c r="J3" s="5">
         <v>0.56820000000000004</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="5">
         <v>0.1646</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="5">
         <v>-0.32019999999999998</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="5">
         <v>-0.38879999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>0.62</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>1.5289999999999999</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>0.80759999999999998</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>-0.49640000000000001</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>-1.2101</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>1.6341000000000001</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <v>1.2968999999999999</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>0.91249999999999998</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <v>-1.8798999999999999</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>1.1647000000000001</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <v>0.48599999999999999</v>
       </c>
-      <c r="M4" s="8"/>
+      <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>-0.55630000000000002</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>0.3009</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>-0.56240000000000001</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>-0.34429999999999999</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>-0.95640000000000003</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>9.4899999999999998E-2</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <v>-0.70079999999999998</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>0.1457</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>-0.17430000000000001</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="5">
         <v>-0.18479999999999999</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="5">
         <v>-1.1009</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="5">
         <v>-0.68400000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>-1.3229</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>-0.42359999999999998</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>-1.8945000000000001</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>-1.6929000000000001</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>-2.2704</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>-1.0939000000000001</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <v>-1.3098000000000001</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>-1.0169999999999999</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <v>-1.7105999999999999</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="5">
         <v>-1.7777000000000001</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <v>-1.9029</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="5">
         <v>-1.3284</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>-0.66849999999999998</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7">
+      <c r="C7" s="6"/>
+      <c r="D7" s="5">
         <v>-0.43219999999999997</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>-0.1191</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>-0.38300000000000001</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>0.26929999999999998</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <v>-7.5700000000000003E-2</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <v>0.59750000000000003</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7">
+      <c r="J7" s="6"/>
+      <c r="K7" s="5">
         <v>-0.3216</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="5">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="5">
         <v>0.4778</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>-0.63119999999999998</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>-1.9643999999999999</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>-2.0152000000000001</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>0.12740000000000001</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>-1.2509999999999999</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <v>-1.7951999999999999</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="5">
         <v>-1.6484000000000001</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <v>-0.91759999999999997</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="5">
         <v>-8.7400000000000005E-2</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="5">
         <v>-1.7803</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="5">
         <v>-1.4346000000000001</v>
       </c>
-      <c r="M8" s="8"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>-0.3518</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>0.31009999999999999</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>-0.15890000000000001</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>0.58689999999999998</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="5">
         <v>0.48599999999999999</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="5">
         <v>0.43419999999999997</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="5">
         <v>1.0717000000000001</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="5">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="5">
         <v>1.1548</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="5">
         <v>0.54459999999999997</v>
       </c>
-      <c r="M9" s="8"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>6.3299999999999995E-2</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>0.17119999999999999</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>-1.9531000000000001</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>-0.21510000000000001</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>-1.4630000000000001</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="5">
         <v>0.30249999999999999</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="5">
         <v>-2.2646000000000002</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <v>1.4417</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <v>-1.2318</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="5">
         <v>-0.14030000000000001</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="5">
         <v>-1.9814000000000001</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="5">
         <v>-1.2117</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>-0.91690000000000005</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>1.2958000000000001</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>0.42699999999999999</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>-7.1199999999999999E-2</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>1.5911</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <v>1.2565999999999999</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <v>0.39100000000000001</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="5">
         <v>-0.31259999999999999</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="5">
         <v>1.5823</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="5">
         <v>2.7766999999999999</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="5">
         <v>0.9466</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="5">
         <v>1.4664999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="7">
+      <c r="B12" s="7"/>
+      <c r="C12" s="5">
         <v>-0.54890000000000005</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>0.24909999999999999</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>0.90359999999999996</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>-0.5302</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>1.6E-2</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <v>-9.9699999999999997E-2</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>1.0787</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="5">
         <v>-0.1371</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="5">
         <v>0.40110000000000001</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="5">
         <v>6.0299999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>0.47260000000000002</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>1.1254999999999999</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>0.62629999999999997</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>0.52559999999999996</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>-0.33250000000000002</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <v>1.6525000000000001</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="5">
         <v>-0.1135</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <v>0.61</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="5">
         <v>0.67210000000000003</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="5">
         <v>0.95820000000000005</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="5">
         <v>0.31269999999999998</v>
       </c>
-      <c r="M13" s="8"/>
+      <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>-0.4763</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7">
+      <c r="C14" s="6"/>
+      <c r="D14" s="5">
         <v>-0.33360000000000001</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>-0.54890000000000005</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>2.5266000000000002</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>0.40410000000000001</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <v>2.5700000000000001E-2</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>-0.2142</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <v>-0.31009999999999999</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="5">
         <v>0.90500000000000003</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="5">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="5">
         <v>0.23119999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>-1.2421</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>0.33439999999999998</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>-0.73499999999999999</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>0.29349999999999998</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>-1.2684</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <v>-0.87819999999999998</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="5">
         <v>1.0021</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>-0.76680000000000004</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="5">
         <v>0.97960000000000003</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="5">
         <v>-5.28E-2</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="5">
         <v>-0.86929999999999996</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="5">
         <v>0.55789999999999995</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>-1.3433999999999999</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>-0.93540000000000001</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>-1.7083999999999999</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>-0.28220000000000001</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>-5.8900000000000001E-2</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>-0.71579999999999999</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <v>-0.11550000000000001</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>-2.4802</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <v>0.66569999999999996</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="5">
         <v>0.53159999999999996</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="5">
         <v>-1.3987000000000001</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="5">
         <v>0.29849999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>0.83440000000000003</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>0.83979999999999999</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>0.91839999999999999</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>0.47470000000000001</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <v>2.3845000000000001</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="5">
         <v>0.1525</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="5">
         <v>0.65110000000000001</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <v>-0.82630000000000003</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="5">
         <v>0.31130000000000002</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="5">
         <v>-9.06E-2</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="5">
         <v>0.96989999999999998</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="5">
         <v>-4.41E-2</v>
       </c>
     </row>
@@ -11704,732 +11704,704 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.875" style="2"/>
+    <col min="1" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1">
         <v>15</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>15</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <v>15</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="1">
         <v>15</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1">
         <v>30</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="1">
         <v>30</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <v>30</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="1">
         <v>30</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <v>60</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="1">
         <v>60</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="1">
         <v>60</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
         <v>-0.47960000000000003</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>-0.84460000000000002</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>0.71089999999999998</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>-0.51019999999999999</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>-0.73140000000000005</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>-2.4274</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>-0.80579999999999996</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>-0.2853</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>-0.6946</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <v>0.53200000000000003</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>-1.9781</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1">
         <v>-2.1126999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>-0.8095</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>-0.62429999999999997</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>-1.1295999999999999</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>-1.1113</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>-1.4079999999999999</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>2.6021000000000001</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>-0.40789999999999998</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>1.2345999999999999</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>1.1846000000000001</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>-5.8799999999999998E-2</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>0.44040000000000001</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>-0.1933</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>0.93859999999999999</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>1.6431</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>1.3142</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>2.0192999999999999</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>1.8205</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>3.1194999999999999</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>0.32229999999999998</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>0.73740000000000006</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>2.1543999999999999</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>0.4506</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <v>-0.1948</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="1">
         <v>0.43</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>-0.40400000000000003</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>0.28260000000000002</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>-0.40579999999999999</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>0.40210000000000001</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>0.8952</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>-1.6909000000000001</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>0.3644</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>-1.1009</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>-0.25580000000000003</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <v>-0.71079999999999999</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>-1.4318</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <v>-0.5121</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>-1.0181</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>-0.38129999999999997</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>0.51639999999999997</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>-0.17</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>0.40560000000000002</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>-0.31390000000000001</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>-1.1147</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <v>-0.92820000000000003</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>0.90890000000000004</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>-0.51359999999999995</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>-0.67430000000000001</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <v>-1.3101</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>1.452</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>0.36680000000000001</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>0.14649999999999999</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>1.0023</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>1.6619999999999999</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>2.9944999999999999</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>1.3996</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <v>1.9426000000000001</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>0.29120000000000001</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <v>0.62819999999999998</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>3.2391000000000001</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <v>2.5788000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>-0.77339999999999998</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>-1.3857999999999999</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>-1.3995</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>-0.61570000000000003</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>-9.8900000000000002E-2</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>0.1457</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>-1.8100000000000002E-2</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <v>-0.54210000000000003</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>-0.44230000000000003</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>-0.41189999999999999</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <v>-0.79379999999999995</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <v>-4.3327</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>0.59570000000000001</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>0.85489999999999999</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>-0.67589999999999995</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>0.63429999999999997</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>-8.6099999999999996E-2</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>-1.0684</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>0.30230000000000001</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <v>0.41770000000000002</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>0.1085</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>-0.44600000000000001</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>0.80179999999999996</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <v>-0.161</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>3.3136000000000001</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>1.8683000000000001</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>0.90639999999999998</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>0.2848</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>1.2425999999999999</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>1.4451000000000001</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>0.91479999999999995</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <v>-1.32E-2</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>1.2979000000000001</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <v>0.10589999999999999</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>-0.29759999999999998</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <v>0.22559999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>0.97719999999999996</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>1.4618</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>-0.71560000000000001</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>0.78990000000000005</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>1.5734999999999999</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>1.1125</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>1.1015999999999999</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <v>0.51459999999999995</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>1.3432999999999999</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <v>0.95009999999999994</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>1.5648</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <v>1.7134</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>1.0774999999999999</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>-1.2575000000000001</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>0.96560000000000001</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>0.16689999999999999</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>0.93940000000000001</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>0.64170000000000005</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>0.58140000000000003</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="1">
         <v>2.5089000000000001</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>0.85389999999999999</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="1">
         <v>1.4608000000000001</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <v>0.77939999999999998</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="1">
         <v>-0.28699999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>-0.41570000000000001</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>0.88400000000000001</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>1.2987</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>1.3915999999999999</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>1.0549999999999999</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>-0.64339999999999997</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>2.4701</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>2.3169</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>1.2747999999999999</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="1">
         <v>1.2483</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <v>0.23849999999999999</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="1">
         <v>1.2221</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>0.1741</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>-0.5323</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>-1.2532000000000001</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>-8.0500000000000002E-2</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>-0.3044</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>0.44</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>-1.0186999999999999</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="1">
         <v>-0.56210000000000004</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>-0.88380000000000003</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="1">
         <v>0.9617</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1">
         <v>-0.89629999999999999</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="1">
         <v>-0.27239999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>-0.70220000000000005</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>0.54079999999999995</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>-4.4299999999999999E-2</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>0.54059999999999997</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>0.81179999999999997</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>0.91839999999999999</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>2.4355000000000002</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="1">
         <v>1.1496</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>1.0065999999999999</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="1">
         <v>-0.29620000000000002</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="1">
         <v>0.35639999999999999</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="1">
         <v>1.0390999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="2">
+      <c r="B16" s="4"/>
+      <c r="C16" s="1">
         <v>0.56440000000000001</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>-1.9400000000000001E-2</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>0.82110000000000005</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>1.1649</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="1">
         <v>0.37130000000000002</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>0.6099</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
         <v>0.92059999999999997</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>0.9647</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="1">
         <v>0.49099999999999999</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>0.92530000000000001</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="1">
         <v>1.2979000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>-1.2206999999999999</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>-0.22620000000000001</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="2">
+      <c r="D17" s="4"/>
+      <c r="E17" s="1">
         <v>0.40500000000000003</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>-0.59819999999999995</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>1.7576000000000001</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="2">
+      <c r="H17" s="4"/>
+      <c r="I17" s="1">
         <v>1.3798999999999999</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>-1.6435999999999999</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="1">
         <v>-0.5111</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="1">
         <v>-1.0851999999999999</v>
       </c>
-      <c r="M17" s="5"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="M17" s="4"/>
     </row>
   </sheetData>
-  <sortState ref="A18:B33">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:B33">
     <sortCondition ref="B18:B33"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12443,700 +12415,700 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1">
         <v>15</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>15</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <v>15</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="1">
         <v>15</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1">
         <v>30</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="1">
         <v>30</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <v>30</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="1">
         <v>30</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <v>60</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="1">
         <v>60</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="1">
         <v>60</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
         <v>-1.393</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>-1.0013000000000001</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>-1.3292999999999999</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>-0.78459999999999996</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>-1.6443000000000001</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>-0.78520000000000001</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>-1.4369000000000001</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>-0.84489999999999998</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>-2.7027000000000001</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <v>-2.6894999999999998</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>-2.8130000000000002</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1">
         <v>-1.7587999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>-0.55800000000000005</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>-0.313</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>-8.8599999999999998E-2</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>0.56740000000000002</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>-0.44800000000000001</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>-0.4768</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>-0.59799999999999998</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>-0.1176</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>-0.27829999999999999</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>-0.60829999999999995</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>-0.6331</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>0.19850000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>1.1608000000000001</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>1.7705</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>2.3542999999999998</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>3.4594999999999998</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>1.3275999999999999</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>1.9211</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>1.6475</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>2.9310999999999998</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>3.6200000000000003E-2</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>0.62390000000000001</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <v>0.90920000000000001</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="1">
         <v>1.0931</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>0.32700000000000001</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>-1.0940000000000001</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>0.37009999999999998</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>-0.53100000000000003</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>-1.5844</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>-0.57079999999999997</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>-0.5494</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>-0.67290000000000005</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <v>-1.867</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>-0.16639999999999999</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <v>-1.3677999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>-1.5401</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>-5.2299999999999999E-2</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>-0.7026</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>-0.49330000000000002</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>-0.81669999999999998</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>-2.8E-3</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>-0.65680000000000005</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <v>-1.0266999999999999</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>-1.9866999999999999</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>-1.5253000000000001</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>-1.0837000000000001</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <v>-1.5982000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>-0.39429999999999998</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>3.0979999999999999</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>-0.78180000000000005</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>0.53659999999999997</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>1.0477000000000001</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>1.9388000000000001</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>1.9984999999999999</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <v>1.948</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>2.8677999999999999</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <v>3.26</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>2.2513000000000001</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <v>1.9187000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>0.3518</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>-6.7100000000000007E-2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>1.5615000000000001</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>-0.51549999999999996</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>0.13589999999999999</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>-0.6129</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>0.46310000000000001</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <v>-0.72570000000000001</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>0.37830000000000003</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>0.4587</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <v>-0.8931</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <v>-0.53600000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>-0.41689999999999999</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>0.6492</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>-0.12590000000000001</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>0.71489999999999998</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>4.5699999999999998E-2</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>0.29320000000000002</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>-0.3901</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <v>0.2321</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>0.92379999999999995</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>0.31740000000000002</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>-2.52E-2</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <v>1.0246</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>0.41020000000000001</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>-0.92030000000000001</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>0.37859999999999999</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>-0.81689999999999996</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>3.0099999999999998E-2</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>-1.4461999999999999</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>-0.30249999999999999</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <v>-0.37269999999999998</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>-0.2195</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <v>-1.1638999999999999</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>0.26190000000000002</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <v>-0.52849999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>2.9630999999999998</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>1.0226999999999999</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>-1.8079000000000001</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>2.6496</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>1.8896999999999999</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>1.3274999999999999</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <v>-2.4363000000000001</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>1.3018000000000001</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <v>-0.26040000000000002</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>2.3205</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <v>-0.2676</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>0.83460000000000001</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>0.54579999999999995</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>-0.40350000000000003</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>0.5827</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>1.0075000000000001</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>0.80379999999999996</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>1.1451</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="1">
         <v>0.6532</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>1.4213</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="1">
         <v>0.75490000000000002</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <v>0.33239999999999997</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="1">
         <v>0.34039999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>0.47499999999999998</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>0.89349999999999996</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>3.44E-2</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>0.92530000000000001</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>-0.28220000000000001</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>0.8125</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>0.4466</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>0.3866</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>-0.1762</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="1">
         <v>0.49059999999999998</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <v>0.49409999999999998</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="1">
         <v>0.45229999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>0.85699999999999998</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>0.39439999999999997</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>-1.01E-2</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>-0.85629999999999995</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>-0.1573</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>-0.13389999999999999</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>-0.1171</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="2">
+      <c r="I14" s="4"/>
+      <c r="J14" s="1">
         <v>0.3775</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="1">
         <v>0.45390000000000003</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1">
         <v>0.33310000000000001</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="1">
         <v>0.20960000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>-0.87780000000000002</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>-0.54210000000000003</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>-1.4449000000000001</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>-0.64190000000000003</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>-0.98599999999999999</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>-2.24E-2</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>-0.44590000000000002</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="1">
         <v>-0.13830000000000001</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>0.93240000000000001</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="1">
         <v>1.2888999999999999</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="1">
         <v>0.65710000000000002</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="1">
         <v>0.97740000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>-1.7099</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>-1.3897999999999999</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>-2.1356000000000002</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>-1.6841999999999999</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>-0.12379999999999999</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="1">
         <v>-1.0174000000000001</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>0.37</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
         <v>-1.6722999999999999</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>-0.25900000000000001</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="1">
         <v>-0.20080000000000001</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>-1.5284</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="1">
         <v>-1.0412999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>-1.903</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="2">
+      <c r="C17" s="4"/>
+      <c r="D17" s="1">
         <v>1.5545</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>-8.4900000000000003E-2</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>-0.61270000000000002</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>1.2343</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>-0.58879999999999999</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="1">
         <v>-0.87460000000000004</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>-0.88219999999999998</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="1">
         <v>0.6754</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="1">
         <v>-0.73409999999999997</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="1">
         <v>-0.5958</v>
       </c>
     </row>
@@ -13152,7 +13124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -13160,696 +13132,696 @@
       <c r="A1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="17">
+      <c r="B1" s="15">
         <v>15</v>
       </c>
-      <c r="C1" s="17">
+      <c r="C1" s="15">
         <v>15</v>
       </c>
-      <c r="D1" s="17">
+      <c r="D1" s="15">
         <v>15</v>
       </c>
-      <c r="E1" s="17">
+      <c r="E1" s="15">
         <v>15</v>
       </c>
-      <c r="F1" s="17">
+      <c r="F1" s="15">
         <v>30</v>
       </c>
-      <c r="G1" s="17">
+      <c r="G1" s="15">
         <v>30</v>
       </c>
-      <c r="H1" s="17">
+      <c r="H1" s="15">
         <v>30</v>
       </c>
-      <c r="I1" s="17">
+      <c r="I1" s="15">
         <v>30</v>
       </c>
-      <c r="J1" s="17">
+      <c r="J1" s="15">
         <v>60</v>
       </c>
-      <c r="K1" s="17">
+      <c r="K1" s="15">
         <v>60</v>
       </c>
-      <c r="L1" s="17">
+      <c r="L1" s="15">
         <v>60</v>
       </c>
-      <c r="M1" s="17">
+      <c r="M1" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="17">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15">
         <v>-0.93340000000000001</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="15">
         <v>-0.49109999999999998</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="15">
         <v>-1.0347</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="15">
         <v>-5.4300000000000001E-2</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="15">
         <v>-2.8940000000000001</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="15">
         <v>-0.88290000000000002</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="15">
         <v>-0.53500000000000003</v>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="15">
         <v>0.129</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="15">
         <v>-2.5434000000000001</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K2" s="15">
         <v>-1.8429</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L2" s="15">
         <v>0.9224</v>
       </c>
-      <c r="M2" s="17">
+      <c r="M2" s="15">
         <v>-0.4647</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="15">
         <v>0.2392</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="15">
         <v>-0.3695</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="15">
         <v>-1.0907</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="15">
         <v>0.17549999999999999</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="15">
         <v>0.52700000000000002</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="15">
         <v>-0.19889999999999999</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="15">
         <v>-0.95930000000000004</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="15">
         <v>-0.2329</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="15">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="15">
         <v>-0.49980000000000002</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="15">
         <v>-0.29909999999999998</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="15">
         <v>-0.23880000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="15">
         <v>0.71870000000000001</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="15">
         <v>1.6315</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="15">
         <v>3.2448000000000001</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="15">
         <v>-3.2275</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="15">
         <v>-2.3641000000000001</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="15">
         <v>2.2749999999999999</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="15">
         <v>0.9244</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="15">
         <v>-2.6962999999999999</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="15">
         <v>0.31990000000000002</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="15">
         <v>2.9540999999999999</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="15">
         <v>-0.8337</v>
       </c>
-      <c r="M4" s="17">
+      <c r="M4" s="15">
         <v>-2.5552000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="15">
         <v>0.36799999999999999</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="15">
         <v>-0.10440000000000001</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="15">
         <v>7.6E-3</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="15">
         <v>-0.97260000000000002</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="15">
         <v>-8.8400000000000006E-2</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="15">
         <v>-1.1843999999999999</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="15">
         <v>-0.51300000000000001</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="15">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="15">
         <v>-1.7664</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="15">
         <v>-2.3744000000000001</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="15">
         <v>-0.42449999999999999</v>
       </c>
-      <c r="M5" s="17">
+      <c r="M5" s="15">
         <v>-0.59099999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>0.27179999999999999</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="15">
         <v>1.0969</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="15">
         <v>8.2500000000000004E-2</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="15">
         <v>-0.43659999999999999</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="15">
         <v>-2.2907000000000002</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="15">
         <v>0.50260000000000005</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="15">
         <v>-0.27150000000000002</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="15">
         <v>-0.57410000000000005</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="15">
         <v>-1.5159</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="15">
         <v>0.42109999999999997</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="15">
         <v>1.7901</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="15">
         <v>-0.87539999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="15">
         <v>0.62390000000000001</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="15">
         <v>0.81840000000000002</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="15">
         <v>1.4916</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="15">
         <v>-0.8397</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="15">
         <v>0.88670000000000004</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="15">
         <v>1.2386999999999999</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="15">
         <v>2.2606000000000002</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="15">
         <v>0.32929999999999998</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="15">
         <v>1.2067000000000001</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="15">
         <v>1.7983</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="15">
         <v>-0.70660000000000001</v>
       </c>
-      <c r="M7" s="17">
+      <c r="M7" s="15">
         <v>1.0147999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="15">
         <v>1.1274999999999999</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="15">
         <v>-0.15479999999999999</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="15">
         <v>0.15390000000000001</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="15">
         <v>-1.8301000000000001</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="15">
         <v>-0.82740000000000002</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="15">
         <v>-8.3599999999999994E-2</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="15">
         <v>0.62150000000000005</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="15">
         <v>-0.80579999999999996</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="15">
         <v>0.55489999999999995</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="15">
         <v>-0.25569999999999998</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="15">
         <v>-1.5242</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="15">
         <v>-1.1165</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="15">
         <v>-0.39379999999999998</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="15">
         <v>7.8600000000000003E-2</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="15">
         <v>-0.97989999999999999</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="15">
         <v>0.36030000000000001</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="15">
         <v>-0.56820000000000004</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="15">
         <v>-7.2800000000000004E-2</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="15">
         <v>-0.186</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="15">
         <v>0.63060000000000005</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="15">
         <v>0.29170000000000001</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="15">
         <v>-0.1706</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="15">
         <v>0.29249999999999998</v>
       </c>
-      <c r="M9" s="17">
+      <c r="M9" s="15">
         <v>0.89139999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="15">
         <v>0.2944</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="15">
         <v>-1.0325</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="15">
         <v>-0.34420000000000001</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="15">
         <v>0.89370000000000005</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <v>-1.5780000000000001</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="15">
         <v>-1.4498</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="15">
         <v>-0.73839999999999995</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="15">
         <v>-0.2666</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="15">
         <v>-1.5417000000000001</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="15">
         <v>-3.0545</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="15">
         <v>1.8973</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="15">
         <v>-0.88439999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="15">
         <v>1.0058</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="15">
         <v>-3.1699999999999999E-2</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="15">
         <v>2.0181</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="15">
         <v>0.78879999999999995</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <v>-0.20660000000000001</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="15">
         <v>0.3846</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="15">
         <v>9.1399999999999995E-2</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="15">
         <v>0.1787</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="15">
         <v>0.1767</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="15">
         <v>0.48980000000000001</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="15">
         <v>0.83540000000000003</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="15">
         <v>0.46439999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <v>-0.32290000000000002</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="15">
         <v>-0.37169999999999997</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="15">
         <v>-0.80130000000000001</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="15">
         <v>0.4516</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <v>-0.37780000000000002</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="15">
         <v>-0.32479999999999998</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="15">
         <v>-0.47610000000000002</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="15">
         <v>0.95050000000000001</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="15">
         <v>-0.2303</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="15">
         <v>-0.56030000000000002</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="15">
         <v>1.2226999999999999</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="15">
         <v>0.57889999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <v>1.2329000000000001</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="15">
         <v>2.2441</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="15">
         <v>0.49480000000000002</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="15">
         <v>-0.69450000000000001</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <v>-0.83460000000000001</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="15">
         <v>1.8561000000000001</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <v>-0.52869999999999995</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="15">
         <v>-0.60660000000000003</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="15">
         <v>0.99839999999999995</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="15">
         <v>1.3966000000000001</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="15">
         <v>-0.15140000000000001</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="15">
         <v>-0.58509999999999995</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="15">
         <v>0.52490000000000003</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="15">
         <v>0.1762</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="15">
         <v>-0.16950000000000001</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="15">
         <v>0.33610000000000001</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <v>1.0117</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="15">
         <v>-0.54710000000000003</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="15">
         <v>-0.14910000000000001</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="15">
         <v>0.26079999999999998</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="15">
         <v>0.74080000000000001</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="15">
         <v>-0.57830000000000004</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="15">
         <v>0.45569999999999999</v>
       </c>
-      <c r="M14" s="17">
+      <c r="M14" s="15">
         <v>0.52290000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="15">
         <v>-0.182</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="15">
         <v>-1.0702</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="15">
         <v>-0.84470000000000001</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="15">
         <v>-1.0067999999999999</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="15">
         <v>0.1177</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="15">
         <v>-0.35110000000000002</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="15">
         <v>2.24E-2</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="15">
         <v>-0.61650000000000005</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="15">
         <v>0.77029999999999998</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="15">
         <v>-1.1442000000000001</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="15">
         <v>-0.80579999999999996</v>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="15">
         <v>0.14030000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="15">
         <v>-2.4929000000000001</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="15">
         <v>-0.45329999999999998</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="15">
         <v>-0.22650000000000001</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="15">
         <v>-1.1136999999999999</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="15">
         <v>-0.91169999999999995</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="15">
         <v>-0.248</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="15">
         <v>-7.8299999999999995E-2</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="15">
         <v>-1.7543</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="15">
         <v>-0.77810000000000001</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="15">
         <v>-0.3231</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="15">
         <v>0.2596</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="15">
         <v>-2.0924</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="15">
         <v>-0.23080000000000001</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="15">
         <v>-0.39169999999999999</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="15">
         <v>-1.0017</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="15">
         <v>0.17660000000000001</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="15">
         <v>1.17E-2</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="15">
         <v>0.17510000000000001</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <v>-0.97560000000000002</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="15">
         <v>-0.53039999999999998</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="15">
         <v>0.44109999999999999</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="15">
         <v>-0.70899999999999996</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="15">
         <v>-9.9000000000000008E-3</v>
       </c>
-      <c r="M17" s="17">
+      <c r="M17" s="15">
         <v>0.84150000000000003</v>
       </c>
     </row>
@@ -13859,694 +13831,694 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1">
         <v>15</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>15</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <v>15</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="1">
         <v>15</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1">
         <v>30</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="1">
         <v>30</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <v>30</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="1">
         <v>30</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <v>60</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="1">
         <v>60</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="1">
         <v>60</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
         <v>-0.82979999999999998</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>4.1099999999999998E-2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>-2.5891000000000002</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>0.2324</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>1.1996</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>-0.84909999999999997</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>-1.5457000000000001</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>-2.3052999999999999</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>9.4299999999999995E-2</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <v>-1.9066000000000001</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>-1.7317</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1">
         <v>-3.6926999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>-0.27779999999999999</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>-0.80400000000000005</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>-0.38350000000000001</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>0.32800000000000001</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>-0.64180000000000004</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>-0.80030000000000001</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>-3.4693000000000001</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>-1.458</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>0.2762</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>-0.74109999999999998</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>-1.2214</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>-0.53690000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>1.7266999999999999</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>2.5236000000000001</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>1.8438000000000001</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>0.90859999999999996</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>-0.10580000000000001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>1.2846</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>1.0021</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>0.75580000000000003</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>0.54990000000000006</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>-8.4199999999999997E-2</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>-1.3079000000000001</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>-0.26369999999999999</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>-0.17199999999999999</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>0.27210000000000001</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>-0.13300000000000001</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>-1.1892</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>-1.84E-2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>-0.99729999999999996</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>-1.4568000000000001</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <v>-1.3769</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>-0.75129999999999997</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <v>-1.6518999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1.3934</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>-0.54239999999999999</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>0.21049999999999999</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>2.8875000000000002</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>0.64729999999999999</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>-0.81430000000000002</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>0.2084</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <v>-0.89510000000000001</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>-7.9399999999999998E-2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>-1.7999000000000001</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>-0.441</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <v>-1.2416</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="2">
+      <c r="B7" s="4"/>
+      <c r="C7" s="1">
         <v>2.4161999999999999</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>1.1740999999999999</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>0.74129999999999996</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>1.7565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>2.5972</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>0.86929999999999996</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <v>2.4257</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>1.5716000000000001</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <v>3.7502</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>2.3832</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <v>2.6749999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>0.44290000000000002</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>0.2792</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>-2.4299999999999999E-2</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>0.29210000000000003</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>-0.5776</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>-0.3785</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>0.99080000000000001</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <v>0.13869999999999999</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>-0.43009999999999998</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>-0.79359999999999997</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <v>0.13850000000000001</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <v>0.30680000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>0.49440000000000001</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>0.64149999999999996</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>-0.12570000000000001</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>0.93879999999999997</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>0.66839999999999999</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>0.42559999999999998</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>0.19800000000000001</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <v>0.5877</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>0.58540000000000003</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>0.17799999999999999</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <v>1.0084</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>0.9889</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>1.6616</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>0.5464</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>1.3427</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>-0.31390000000000001</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>0.246</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <v>-1.8160000000000001</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>-0.1356</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <v>-0.63580000000000003</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>-0.21690000000000001</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <v>-1.1214</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>0.35189999999999999</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>1.4939</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>2.1932999999999998</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>0.75609999999999999</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>0.39610000000000001</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>1.6777</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>1.8124</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <v>0.72519999999999996</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>1.1679999999999999</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <v>2.1741000000000001</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>2.2208999999999999</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <v>2.0417000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>-0.14549999999999999</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>0.7077</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>-0.35189999999999999</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>0.97850000000000004</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>1.0745</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>0.53269999999999995</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>0.50319999999999998</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="1">
         <v>1.0996999999999999</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>1.1006</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="1">
         <v>0.46260000000000001</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <v>-0.2581</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="1">
         <v>0.84799999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>0.55179999999999996</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>0.69489999999999996</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>0.4098</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>0.55769999999999997</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>0.82</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>1.0041</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>1.3720000000000001</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>1.4371</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>-0.68630000000000002</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <v>1E-4</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <v>0.34949999999999998</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="1">
         <v>0.55059999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>-3.8899999999999997E-2</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>-0.93069999999999997</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>0.49580000000000002</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>-1.9599999999999999E-2</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>0.4521</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>-0.60529999999999995</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>-0.79879999999999995</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="1">
         <v>-0.1749</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>0.30059999999999998</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="1">
         <v>9.0899999999999995E-2</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1">
         <v>-0.78659999999999997</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="1">
         <v>0.2419</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>-0.70609999999999995</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>-0.84360000000000002</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>-2.1758000000000002</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>-1.6096999999999999</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>-0.74219999999999997</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>0.48330000000000001</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>0.61160000000000003</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="1">
         <v>-8.3500000000000005E-2</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>-0.44540000000000002</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="1">
         <v>0.34720000000000001</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="1">
         <v>0.74909999999999999</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="1">
         <v>0.69569999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>-1.7194</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>-0.49790000000000001</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>-1.2355</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>-1.9155</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>-0.51780000000000004</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="1">
         <v>0.62549999999999994</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>-0.89380000000000004</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
         <v>-0.50629999999999997</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>-1.0351999999999999</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="1">
         <v>0.85160000000000002</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>-0.3387</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="1">
         <v>-1.0581</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="2">
+      <c r="B17" s="4"/>
+      <c r="C17" s="1">
         <v>0.12870000000000001</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>0.7379</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>0.76519999999999999</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>-1.2347999999999999</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>-0.2555</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>-5.0620000000000003</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="1">
         <v>-0.23730000000000001</v>
       </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="2">
+      <c r="J17" s="4"/>
+      <c r="K17" s="1">
         <v>0.69140000000000001</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="1">
         <v>-2.6760000000000002</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="1">
         <v>-0.8246</v>
       </c>
     </row>
@@ -14562,908 +14534,908 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2">
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
         <v>1</v>
       </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2">
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>1</v>
       </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
         <v>1</v>
       </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2">
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2">
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>1</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>1</v>
       </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>1</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>1</v>
       </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
         <v>1</v>
       </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2">
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>1</v>
       </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2">
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
         <v>1</v>
       </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2">
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
         <v>1</v>
       </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="2">
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
         <v>1</v>
       </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2">
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
         <v>1</v>
       </c>
-      <c r="M13" s="2">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="2">
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2">
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="M14" s="2">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="2">
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>1</v>
       </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2">
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
         <v>1</v>
       </c>
-      <c r="M15" s="2">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2">
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
         <v>1</v>
       </c>
-      <c r="O15" s="2">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="2">
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2">
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>1</v>
       </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2">
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
         <v>1</v>
       </c>
-      <c r="O16" s="2">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="2">
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2">
-        <v>0</v>
-      </c>
-      <c r="O17" s="2">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="2">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
         <v>0</v>
       </c>
     </row>
